--- a/artfynd/A 30872-2026 artfynd.xlsx
+++ b/artfynd/A 30872-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135515738</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,8 +886,138 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135515718</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135577813</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kareby, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>318632</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6421862</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135577813</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30872-2026 artfynd.xlsx
+++ b/artfynd/A 30872-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135515738</v>
       </c>
       <c r="B2" t="n">
-        <v>96783</v>
+        <v>96827</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135515718</v>
       </c>
       <c r="B3" t="n">
-        <v>96512</v>
+        <v>96556</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135577813</v>
       </c>
       <c r="B4" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30872-2026 artfynd.xlsx
+++ b/artfynd/A 30872-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135515738</v>
       </c>
       <c r="B2" t="n">
-        <v>96827</v>
+        <v>96854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135515718</v>
       </c>
       <c r="B3" t="n">
-        <v>96556</v>
+        <v>96583</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30872-2026 artfynd.xlsx
+++ b/artfynd/A 30872-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135515738</v>
       </c>
       <c r="B2" t="n">
-        <v>96859</v>
+        <v>96861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135515718</v>
       </c>
       <c r="B3" t="n">
-        <v>96588</v>
+        <v>96590</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30872-2026 artfynd.xlsx
+++ b/artfynd/A 30872-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135515738</v>
       </c>
       <c r="B2" t="n">
-        <v>96861</v>
+        <v>96878</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135515718</v>
       </c>
       <c r="B3" t="n">
-        <v>96590</v>
+        <v>96607</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135577813</v>
       </c>
       <c r="B4" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30872-2026 artfynd.xlsx
+++ b/artfynd/A 30872-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135515738</v>
       </c>
       <c r="B2" t="n">
-        <v>96878</v>
+        <v>96879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135515718</v>
       </c>
       <c r="B3" t="n">
-        <v>96607</v>
+        <v>96608</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
